--- a/Excel/035-portfolio.xlsx
+++ b/Excel/035-portfolio.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,37 +497,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PTTGC</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44272</v>
+        <v>44446</v>
       </c>
       <c r="E2" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="F2" t="n">
-        <v>64.75</v>
+        <v>21.7</v>
       </c>
       <c r="G2" t="n">
-        <v>38.75</v>
+        <v>11.4</v>
       </c>
       <c r="H2" t="n">
-        <v>388500</v>
+        <v>86800</v>
       </c>
       <c r="I2" t="n">
-        <v>232500</v>
+        <v>45600</v>
       </c>
       <c r="J2" t="n">
-        <v>-156000</v>
+        <v>-41199.99999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-40.15444015444015</v>
+        <v>-47.46543778801843</v>
       </c>
     </row>
     <row r="3">
@@ -538,37 +538,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SINGER</t>
+          <t>JMT</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>44945</v>
+        <v>44952</v>
       </c>
       <c r="E3" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="F3" t="n">
-        <v>24.8</v>
+        <v>37.7</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8</v>
+        <v>10.6</v>
       </c>
       <c r="H3" t="n">
-        <v>148800</v>
+        <v>263900</v>
       </c>
       <c r="I3" t="n">
-        <v>34800</v>
+        <v>74200</v>
       </c>
       <c r="J3" t="n">
-        <v>-114000</v>
+        <v>-189700</v>
       </c>
       <c r="K3" t="n">
-        <v>-76.61290322580645</v>
+        <v>-71.88328912466844</v>
       </c>
     </row>
     <row r="4">
@@ -579,119 +579,119 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>44362</v>
+        <v>44440</v>
       </c>
       <c r="E4" t="n">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>7.45</v>
       </c>
       <c r="G4" t="n">
-        <v>18.9</v>
+        <v>4.68</v>
       </c>
       <c r="H4" t="n">
-        <v>300000</v>
+        <v>201150</v>
       </c>
       <c r="I4" t="n">
-        <v>189000</v>
+        <v>126360</v>
       </c>
       <c r="J4" t="n">
-        <v>-111000</v>
+        <v>-74790.00000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-37.00000000000001</v>
+        <v>-37.18120805369129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3BBIF</t>
+          <t>PTG</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>43237</v>
+        <v>45119</v>
       </c>
       <c r="E5" t="n">
-        <v>120000</v>
+        <v>3600</v>
       </c>
       <c r="F5" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>8.35</v>
       </c>
       <c r="H5" t="n">
-        <v>1212000</v>
+        <v>41040</v>
       </c>
       <c r="I5" t="n">
-        <v>792000</v>
+        <v>30060</v>
       </c>
       <c r="J5" t="n">
-        <v>-420000</v>
+        <v>-10980</v>
       </c>
       <c r="K5" t="n">
-        <v>-34.65346534653465</v>
+        <v>-26.75438596491229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>44789</v>
+        <v>44362</v>
       </c>
       <c r="E6" t="n">
-        <v>55000</v>
+        <v>10000</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>12.3</v>
+        <v>21.5</v>
       </c>
       <c r="H6" t="n">
-        <v>990000</v>
+        <v>300000</v>
       </c>
       <c r="I6" t="n">
-        <v>676500</v>
+        <v>215000</v>
       </c>
       <c r="J6" t="n">
-        <v>-313499.9999999999</v>
+        <v>-85000</v>
       </c>
       <c r="K6" t="n">
-        <v>-31.66666666666666</v>
+        <v>-28.33333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DIF</t>
+          <t>3BBIF</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>44044</v>
+        <v>43237</v>
       </c>
       <c r="E7" t="n">
-        <v>45000</v>
+        <v>120000</v>
       </c>
       <c r="F7" t="n">
-        <v>12.7</v>
+        <v>10.1</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>6.45</v>
       </c>
       <c r="H7" t="n">
-        <v>571500</v>
+        <v>1212000</v>
       </c>
       <c r="I7" t="n">
-        <v>450000</v>
+        <v>774000</v>
       </c>
       <c r="J7" t="n">
-        <v>-121500</v>
+        <v>-437999.9999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-21.25984251968503</v>
+        <v>-36.13861386138613</v>
       </c>
     </row>
     <row r="8">
@@ -743,37 +743,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GVREIT</t>
+          <t>AIMIRT</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>44797</v>
+        <v>46163</v>
       </c>
       <c r="E8" t="n">
-        <v>69000</v>
+        <v>10000</v>
       </c>
       <c r="F8" t="n">
-        <v>7.75</v>
+        <v>11.3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>12.2</v>
       </c>
       <c r="H8" t="n">
-        <v>534750</v>
+        <v>113000</v>
       </c>
       <c r="I8" t="n">
-        <v>469200</v>
+        <v>122000</v>
       </c>
       <c r="J8" t="n">
-        <v>-65550.00000000001</v>
+        <v>8999.999999999985</v>
       </c>
       <c r="K8" t="n">
-        <v>-12.25806451612903</v>
+        <v>7.964601769911492</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>42633</v>
+        <v>44789</v>
       </c>
       <c r="E9" t="n">
-        <v>75000</v>
+        <v>55000</v>
       </c>
       <c r="F9" t="n">
-        <v>15.4</v>
+        <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>8.25</v>
+        <v>13.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1155000</v>
+        <v>990000</v>
       </c>
       <c r="I9" t="n">
-        <v>618750</v>
+        <v>726000</v>
       </c>
       <c r="J9" t="n">
-        <v>-536250</v>
+        <v>-264000.0000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-46.42857142857143</v>
+        <v>-26.66666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -825,37 +825,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>DIF</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>44440</v>
+        <v>44044</v>
       </c>
       <c r="E10" t="n">
-        <v>27000</v>
+        <v>45000</v>
       </c>
       <c r="F10" t="n">
-        <v>7.45</v>
+        <v>12.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4.32</v>
+        <v>10.1</v>
       </c>
       <c r="H10" t="n">
-        <v>201150</v>
+        <v>571500</v>
       </c>
       <c r="I10" t="n">
-        <v>116640</v>
+        <v>454500</v>
       </c>
       <c r="J10" t="n">
-        <v>-84510</v>
+        <v>-117000</v>
       </c>
       <c r="K10" t="n">
-        <v>-42.01342281879194</v>
+        <v>-20.47244094488189</v>
       </c>
     </row>
     <row r="11">
@@ -866,37 +866,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>GVREIT</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45877</v>
+        <v>44797</v>
       </c>
       <c r="E11" t="n">
-        <v>7500</v>
+        <v>69000</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>7.75</v>
       </c>
       <c r="G11" t="n">
-        <v>36.5</v>
+        <v>7.7</v>
       </c>
       <c r="H11" t="n">
-        <v>240000</v>
+        <v>534750</v>
       </c>
       <c r="I11" t="n">
-        <v>273750</v>
+        <v>531300</v>
       </c>
       <c r="J11" t="n">
-        <v>33750</v>
+        <v>-3449.999999999988</v>
       </c>
       <c r="K11" t="n">
-        <v>14.0625</v>
+        <v>-0.6451612903225784</v>
       </c>
     </row>
     <row r="12">
@@ -907,37 +907,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>44649</v>
+        <v>42633</v>
       </c>
       <c r="E12" t="n">
-        <v>105000</v>
+        <v>75000</v>
       </c>
       <c r="F12" t="n">
-        <v>4.48</v>
+        <v>15.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="H12" t="n">
-        <v>470400</v>
+        <v>1147500</v>
       </c>
       <c r="I12" t="n">
-        <v>216300</v>
+        <v>585000</v>
       </c>
       <c r="J12" t="n">
-        <v>-254100</v>
+        <v>-562500.0000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-54.01785714285715</v>
+        <v>-49.01960784313727</v>
       </c>
     </row>
     <row r="13">
@@ -948,37 +948,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>PROSPECT</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45113</v>
+        <v>46183</v>
       </c>
       <c r="E13" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="F13" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>9.6</v>
       </c>
       <c r="H13" t="n">
-        <v>182500</v>
+        <v>291000</v>
       </c>
       <c r="I13" t="n">
-        <v>162500</v>
+        <v>288000</v>
       </c>
       <c r="J13" t="n">
-        <v>-20000</v>
+        <v>-2999.99999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-10.95890410958904</v>
+        <v>-1.030927835051543</v>
       </c>
     </row>
     <row r="14">
@@ -989,37 +989,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WHAIR</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>44480</v>
+        <v>45877</v>
       </c>
       <c r="E14" t="n">
-        <v>50000</v>
+        <v>7500</v>
       </c>
       <c r="F14" t="n">
-        <v>8.699999999999999</v>
+        <v>32</v>
       </c>
       <c r="G14" t="n">
-        <v>7.65</v>
+        <v>42.25</v>
       </c>
       <c r="H14" t="n">
-        <v>435000</v>
+        <v>240000</v>
       </c>
       <c r="I14" t="n">
-        <v>382500</v>
+        <v>316875</v>
       </c>
       <c r="J14" t="n">
-        <v>-52499.99999999995</v>
+        <v>76875</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.06896551724137</v>
+        <v>32.03125</v>
       </c>
     </row>
     <row r="15">
@@ -1030,160 +1030,160 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WHART</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>44566</v>
+        <v>44649</v>
       </c>
       <c r="E15" t="n">
-        <v>20000</v>
+        <v>105000</v>
       </c>
       <c r="F15" t="n">
-        <v>12.3</v>
+        <v>4.48</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>1.68</v>
       </c>
       <c r="H15" t="n">
-        <v>246000</v>
+        <v>470400</v>
       </c>
       <c r="I15" t="n">
-        <v>216000</v>
+        <v>176400</v>
       </c>
       <c r="J15" t="n">
-        <v>-30000</v>
+        <v>-294000.0000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-12.19512195121951</v>
+        <v>-62.50000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADVANC</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46080</v>
+        <v>45113</v>
       </c>
       <c r="E16" t="n">
-        <v>400</v>
+        <v>30000</v>
       </c>
       <c r="F16" t="n">
-        <v>355</v>
+        <v>7.25</v>
       </c>
       <c r="G16" t="n">
-        <v>350</v>
+        <v>7.15</v>
       </c>
       <c r="H16" t="n">
-        <v>142000</v>
+        <v>217500</v>
       </c>
       <c r="I16" t="n">
-        <v>140000</v>
+        <v>214500</v>
       </c>
       <c r="J16" t="n">
-        <v>-2000</v>
+        <v>-2999.99999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.408450704225352</v>
+        <v>-1.379310344827581</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>WHAIR</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45085</v>
+        <v>44480</v>
       </c>
       <c r="E17" t="n">
-        <v>1200</v>
+        <v>50000</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>44400</v>
+        <v>435000</v>
       </c>
       <c r="I17" t="n">
-        <v>16440</v>
+        <v>434999.9999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-27960</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-62.97297297297298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>WHART</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45092</v>
+        <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="F18" t="n">
-        <v>4.96</v>
+        <v>12.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>11.2</v>
       </c>
       <c r="H18" t="n">
-        <v>44640</v>
+        <v>246000</v>
       </c>
       <c r="I18" t="n">
-        <v>19260</v>
+        <v>224000</v>
       </c>
       <c r="J18" t="n">
-        <v>-25380</v>
+        <v>-22000.00000000003</v>
       </c>
       <c r="K18" t="n">
-        <v>-56.85483870967742</v>
+        <v>-8.94308943089432</v>
       </c>
     </row>
     <row r="19">
@@ -1194,37 +1194,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>ADVANC</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>44446</v>
+        <v>46080</v>
       </c>
       <c r="E19" t="n">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="F19" t="n">
-        <v>21.7</v>
+        <v>355</v>
       </c>
       <c r="G19" t="n">
-        <v>9.300000000000001</v>
+        <v>344</v>
       </c>
       <c r="H19" t="n">
-        <v>86800</v>
+        <v>142000</v>
       </c>
       <c r="I19" t="n">
-        <v>37200</v>
+        <v>137600</v>
       </c>
       <c r="J19" t="n">
-        <v>-49599.99999999999</v>
+        <v>-4400</v>
       </c>
       <c r="K19" t="n">
-        <v>-57.14285714285714</v>
+        <v>-3.098591549295775</v>
       </c>
     </row>
     <row r="20">
@@ -1235,37 +1235,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CPF</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45890</v>
+        <v>45085</v>
       </c>
       <c r="E20" t="n">
-        <v>10000</v>
+        <v>1200</v>
       </c>
       <c r="F20" t="n">
-        <v>23.4</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="H20" t="n">
-        <v>234000</v>
+        <v>44400</v>
       </c>
       <c r="I20" t="n">
-        <v>190000</v>
+        <v>18600</v>
       </c>
       <c r="J20" t="n">
-        <v>-43999.99999999999</v>
+        <v>-25800</v>
       </c>
       <c r="K20" t="n">
-        <v>-18.8034188034188</v>
+        <v>-58.10810810810811</v>
       </c>
     </row>
     <row r="21">
@@ -1276,37 +1276,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PTG</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45119</v>
+        <v>44508</v>
       </c>
       <c r="E21" t="n">
-        <v>3600</v>
+        <v>21000</v>
       </c>
       <c r="F21" t="n">
-        <v>11.4</v>
+        <v>41.5</v>
       </c>
       <c r="G21" t="n">
-        <v>7.75</v>
+        <v>46.75</v>
       </c>
       <c r="H21" t="n">
-        <v>41040</v>
+        <v>871500</v>
       </c>
       <c r="I21" t="n">
-        <v>27900</v>
+        <v>981750</v>
       </c>
       <c r="J21" t="n">
-        <v>-13140</v>
+        <v>110250</v>
       </c>
       <c r="K21" t="n">
-        <v>-32.01754385964913</v>
+        <v>12.65060240963855</v>
       </c>
     </row>
     <row r="22">
@@ -1317,37 +1317,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>SYNEX</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>44508</v>
+        <v>44568</v>
       </c>
       <c r="E22" t="n">
-        <v>27000</v>
+        <v>17500</v>
       </c>
       <c r="F22" t="n">
-        <v>38.78</v>
+        <v>26.4</v>
       </c>
       <c r="G22" t="n">
-        <v>32</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>1047060</v>
+        <v>462000</v>
       </c>
       <c r="I22" t="n">
-        <v>864000</v>
+        <v>167125</v>
       </c>
       <c r="J22" t="n">
-        <v>-183060</v>
+        <v>-294874.9999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-17.48323878287777</v>
+        <v>-63.82575757575756</v>
       </c>
     </row>
     <row r="23">
@@ -1358,37 +1358,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SYNEX</t>
+          <t>TOA</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>44568</v>
+        <v>45175</v>
       </c>
       <c r="E23" t="n">
-        <v>17500</v>
+        <v>1000</v>
       </c>
       <c r="F23" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>9.9</v>
+        <v>15.5</v>
       </c>
       <c r="H23" t="n">
-        <v>462000</v>
+        <v>26000</v>
       </c>
       <c r="I23" t="n">
-        <v>173250</v>
+        <v>15500</v>
       </c>
       <c r="J23" t="n">
-        <v>-288750</v>
+        <v>-10500</v>
       </c>
       <c r="K23" t="n">
-        <v>-62.5</v>
+        <v>-40.38461538461539</v>
       </c>
     </row>
     <row r="24">
@@ -1399,78 +1399,78 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TOA</t>
+          <t>TVO</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45175</v>
+        <v>45602</v>
       </c>
       <c r="E24" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
       <c r="G24" t="n">
-        <v>12.4</v>
+        <v>27.5</v>
       </c>
       <c r="H24" t="n">
-        <v>26000</v>
+        <v>99600</v>
       </c>
       <c r="I24" t="n">
-        <v>12400</v>
+        <v>110000</v>
       </c>
       <c r="J24" t="n">
-        <v>-13600</v>
+        <v>10400.00000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-52.30769230769231</v>
+        <v>10.4417670682731</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TVO</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45602</v>
+        <v>45092</v>
       </c>
       <c r="E25" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="F25" t="n">
-        <v>24.9</v>
+        <v>4.96</v>
       </c>
       <c r="G25" t="n">
-        <v>24.2</v>
+        <v>3.04</v>
       </c>
       <c r="H25" t="n">
-        <v>99600</v>
+        <v>44640</v>
       </c>
       <c r="I25" t="n">
-        <v>96800</v>
+        <v>27360</v>
       </c>
       <c r="J25" t="n">
-        <v>-2799.999999999997</v>
+        <v>-17280</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.811244979919676</v>
+        <v>-38.70967741935484</v>
       </c>
     </row>
     <row r="26">
@@ -1481,37 +1481,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IVL</t>
+          <t>CPF</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>44802</v>
+        <v>45890</v>
       </c>
       <c r="E26" t="n">
-        <v>7200</v>
+        <v>10000</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>23.4</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="H26" t="n">
-        <v>288000</v>
+        <v>234000</v>
       </c>
       <c r="I26" t="n">
-        <v>172800</v>
+        <v>231000</v>
       </c>
       <c r="J26" t="n">
-        <v>-115200</v>
+        <v>-2999.999999999972</v>
       </c>
       <c r="K26" t="n">
-        <v>-40</v>
+        <v>-1.28205128205127</v>
       </c>
     </row>
     <row r="27">
@@ -1522,37 +1522,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JMT</t>
+          <t>IVL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>44952</v>
+        <v>44802</v>
       </c>
       <c r="E27" t="n">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="F27" t="n">
-        <v>37.7</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H27" t="n">
-        <v>263900</v>
+        <v>288000</v>
       </c>
       <c r="I27" t="n">
-        <v>70000</v>
+        <v>208800</v>
       </c>
       <c r="J27" t="n">
-        <v>-193900</v>
+        <v>-79200</v>
       </c>
       <c r="K27" t="n">
-        <v>-73.47480106100797</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="28">
@@ -1581,19 +1581,101 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="H28" t="n">
         <v>450000</v>
       </c>
       <c r="I28" t="n">
-        <v>89500</v>
+        <v>86000</v>
       </c>
       <c r="J28" t="n">
-        <v>-360500</v>
+        <v>-364000</v>
       </c>
       <c r="K28" t="n">
-        <v>-80.11111111111111</v>
+        <v>-80.88888888888889</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTTGC</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>44272</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="G29" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>388500</v>
+      </c>
+      <c r="I29" t="n">
+        <v>285000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-103500</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-26.64092664092664</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SINGER</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>148800</v>
+      </c>
+      <c r="I30" t="n">
+        <v>63000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-85800</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-57.66129032258065</v>
       </c>
     </row>
   </sheetData>
